--- a/Figure S61.xlsx
+++ b/Figure S61.xlsx
@@ -1,23 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\My Drive\Dropbox (University of Michigan)\Relay Project\Amide Couplings\Amide ultraHTE Paper\Submission\Github\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\My Drive\Dropbox (University of Michigan)\Relay Project\Amide Couplings\Amide ultraHTE Paper\Submission\J Med Chem\Revisions\Figures\Figure S61\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01E28703-A73B-47E3-B719-4AF15CB99F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{699D5F2B-6F98-4B43-AE06-B87F56B74323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{EE4E0158-AF0E-4503-ADB1-CD2935B1E97D}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{EE4E0158-AF0E-4503-ADB1-CD2935B1E97D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -398,7 +395,7 @@
                   <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>45</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>54</c:v>
@@ -1361,233 +1358,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Sheet2"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="A2">
-            <v>62</v>
-          </cell>
-          <cell r="B2">
-            <v>20</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3">
-            <v>92</v>
-          </cell>
-          <cell r="B3">
-            <v>44</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4">
-            <v>29</v>
-          </cell>
-          <cell r="B4">
-            <v>65</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>26</v>
-          </cell>
-          <cell r="B5">
-            <v>42</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>94</v>
-          </cell>
-          <cell r="B6">
-            <v>86</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>94</v>
-          </cell>
-          <cell r="B7">
-            <v>60</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>56</v>
-          </cell>
-          <cell r="B8">
-            <v>66</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>100</v>
-          </cell>
-          <cell r="B9">
-            <v>41</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>100</v>
-          </cell>
-          <cell r="B10">
-            <v>46</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>94</v>
-          </cell>
-          <cell r="B11">
-            <v>58</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>100</v>
-          </cell>
-          <cell r="B12">
-            <v>65</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>98</v>
-          </cell>
-          <cell r="B13">
-            <v>77</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>56</v>
-          </cell>
-          <cell r="B14">
-            <v>96</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>88</v>
-          </cell>
-          <cell r="B15">
-            <v>17</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>86</v>
-          </cell>
-          <cell r="B16">
-            <v>55</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>90</v>
-          </cell>
-          <cell r="B17">
-            <v>35</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18">
-            <v>93</v>
-          </cell>
-          <cell r="B18">
-            <v>48</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19">
-            <v>94</v>
-          </cell>
-          <cell r="B19">
-            <v>26</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20">
-            <v>94</v>
-          </cell>
-          <cell r="B20">
-            <v>45</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21">
-            <v>67</v>
-          </cell>
-          <cell r="B21">
-            <v>54</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22">
-            <v>100</v>
-          </cell>
-          <cell r="B22">
-            <v>67</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23">
-            <v>50</v>
-          </cell>
-          <cell r="B23">
-            <v>45</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24">
-            <v>74</v>
-          </cell>
-          <cell r="B24">
-            <v>19</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25">
-            <v>97</v>
-          </cell>
-          <cell r="B25">
-            <v>87</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26">
-            <v>100</v>
-          </cell>
-          <cell r="B26">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27">
-            <v>100</v>
-          </cell>
-          <cell r="B27">
-            <v>45</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -1886,14 +1656,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AA5DE82-DEFA-4587-9048-CCE9C920F80B}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.21875" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1904,7 +1674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>11</v>
       </c>
@@ -1915,7 +1685,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1926,7 +1696,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1937,7 +1707,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>19</v>
       </c>
@@ -1948,7 +1718,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>12</v>
       </c>
@@ -1959,7 +1729,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>22</v>
       </c>
@@ -1970,7 +1740,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>20</v>
       </c>
@@ -1981,7 +1751,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>21</v>
       </c>
@@ -1992,7 +1762,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -2003,7 +1773,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
@@ -2014,7 +1784,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>13</v>
       </c>
@@ -2025,7 +1795,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -2036,7 +1806,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
@@ -2047,7 +1817,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -2058,7 +1828,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
@@ -2069,7 +1839,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -2080,7 +1850,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>11</v>
       </c>
@@ -2091,7 +1861,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>15</v>
       </c>
@@ -2102,7 +1872,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>12</v>
       </c>
@@ -2110,10 +1880,10 @@
         <v>94</v>
       </c>
       <c r="C20">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>16</v>
       </c>
@@ -2124,7 +1894,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>13</v>
       </c>
@@ -2135,7 +1905,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>17</v>
       </c>
@@ -2146,7 +1916,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>14</v>
       </c>
@@ -2157,7 +1927,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>18</v>
       </c>
@@ -2168,7 +1938,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>15</v>
       </c>
@@ -2179,7 +1949,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>16</v>
       </c>
